--- a/reports/pdf_change_20260710.xlsx
+++ b/reports/pdf_change_20260710.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,15 +60,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000070C0"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -93,11 +89,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -165,17 +156,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +551,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 6/7  ·  대기: TIGER</t>
+          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,389억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 8종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 8종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +654,7 @@
         <v>109</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>939340200</v>
+        <v>877815150</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -698,7 +682,7 @@
         <v>60</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4669872000</v>
+        <v>4364004000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -726,7 +710,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1205408000</v>
+        <v>1126456000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -754,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>481241800</v>
+        <v>449721350</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -782,7 +766,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>460266400</v>
+        <v>430119800</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -810,7 +794,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>467204000</v>
+        <v>436603000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -838,7 +822,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1022428800</v>
+        <v>955461600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -866,7 +850,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>384386400</v>
+        <v>359209800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -887,7 +871,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,354억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,303억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -911,7 +895,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -935,7 +919,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,581억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -957,356 +941,78 @@
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 324억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 5종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="17" t="n"/>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>120960000</v>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>2.15%→2.52%</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>204→240</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>채비  (편출)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I27" s="17" t="n">
-        <v>-15907920</v>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>0.05%→0.00%</t>
-        </is>
-      </c>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>34→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>79497600</v>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>5.95%→6.19%</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>669→697</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>삼현  (편출)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I28" s="17" t="n">
-        <v>-68493600</v>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>0.21%→0.00%</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
-        <is>
-          <t>27→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" s="11" t="n">
-        <v>18312000</v>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>7.22%→7.27%</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>629→634</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>기가비스</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I29" s="17" t="n">
-        <v>-73332000</v>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>1.61%→1.38%</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>42→36</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>코스메카코리아  (신규)</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" s="11" t="n">
-        <v>33768000</v>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.11%</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>0→5</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I30" s="17" t="n">
-        <v>-35700000</v>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>3.76%→3.64%</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>168→163</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>50870400</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>2.71%→2.87%</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>68→72</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="14" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 571억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n"/>
-      <c r="C36" s="20" t="n"/>
-      <c r="D36" s="20" t="n"/>
-      <c r="E36" s="20" t="n"/>
-      <c r="F36" s="20" t="n"/>
-      <c r="G36" s="20" t="n"/>
-      <c r="H36" s="20" t="n"/>
-      <c r="I36" s="20" t="n"/>
-      <c r="J36" s="20" t="n"/>
-      <c r="K36" s="20" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="15">
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
-    <mergeCell ref="G25:K25"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>

--- a/reports/pdf_change_20260710.xlsx
+++ b/reports/pdf_change_20260710.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,11 +60,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000070C0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +93,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -156,10 +165,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -551,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -941,78 +957,356 @@
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="17" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 5종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>118116000</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2.04%→2.40%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>204→240</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>채비  (편출)</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>-16010600</v>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>0.05%→0.00%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>34→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>77350000</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>5.64%→5.87%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>669→697</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>삼현  (편출)</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>-77571000</v>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>0.24%→0.00%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>17722500</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>6.80%→6.85%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>629→634</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>-77265000</v>
+      </c>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>1.65%→1.41%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>42→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>코스메카코리아  (신규)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>36337500</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.11%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>0→5</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>-36805000</v>
+      </c>
+      <c r="J30" s="18" t="inlineStr">
+        <is>
+          <t>3.77%→3.66%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>168→163</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>51748000</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2.68%→2.84%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>68→72</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="17" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="17" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>

--- a/reports/pdf_change_20260710.xlsx
+++ b/reports/pdf_change_20260710.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 8종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      당일 2026-07-10  vs  전영업일 2026-07-09      매수 8종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,8 +669,10 @@
       <c r="B6" s="11" t="n">
         <v>109</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>877815150</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -697,8 +699,10 @@
       <c r="B7" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>4364004000</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -725,8 +729,10 @@
       <c r="B8" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>1126456000</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -753,8 +759,10 @@
       <c r="B9" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>449721350</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -781,8 +789,10 @@
       <c r="B10" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>430119800</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -809,8 +819,10 @@
       <c r="B11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>436603000</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -837,8 +849,10 @@
       <c r="B12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>955461600</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -865,8 +879,10 @@
       <c r="B13" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>359209800</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -887,7 +903,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,303억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -911,7 +927,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -935,7 +951,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -959,7 +975,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 5종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      당일 2026-07-10  vs  전영업일 2026-07-09      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1054,12 +1070,14 @@
       <c r="B27" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>118116000</v>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>2.04%→2.40%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1075,12 +1093,14 @@
       <c r="H27" s="17" t="n">
         <v>-34</v>
       </c>
-      <c r="I27" s="17" t="n">
-        <v>-16010600</v>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="18" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1098,12 +1118,14 @@
       <c r="B28" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>77350000</v>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>5.64%→5.87%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1119,12 +1141,14 @@
       <c r="H28" s="17" t="n">
         <v>-27</v>
       </c>
-      <c r="I28" s="17" t="n">
-        <v>-77571000</v>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="18" t="inlineStr">
         <is>
-          <t>0.24%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -1142,12 +1166,14 @@
       <c r="B29" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>17722500</v>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>6.80%→6.85%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1163,12 +1189,14 @@
       <c r="H29" s="17" t="n">
         <v>-6</v>
       </c>
-      <c r="I29" s="17" t="n">
-        <v>-77265000</v>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="18" t="inlineStr">
         <is>
-          <t>1.65%→1.41%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1186,12 +1214,14 @@
       <c r="B30" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>36337500</v>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1207,12 +1237,14 @@
       <c r="H30" s="17" t="n">
         <v>-5</v>
       </c>
-      <c r="I30" s="17" t="n">
-        <v>-36805000</v>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="18" t="inlineStr">
         <is>
-          <t>3.77%→3.66%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -1230,12 +1262,14 @@
       <c r="B31" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>51748000</v>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.84%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1252,7 +1286,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      당일 2026-07-10  vs  전영업일 2026-07-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
